--- a/data/trans_orig/P1438_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otro dolor crónico en 2023</t>
+          <t>Población con diagnóstico de otro dolor crónico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33852</t>
+          <t>34961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>58876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64457</t>
+          <t>63878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86422</t>
+          <t>85812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103544</t>
+          <t>105370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135750</t>
+          <t>135927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>578184</t>
+          <t>576565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>601589</t>
+          <t>600480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>588948</t>
+          <t>589558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>610913</t>
+          <t>611492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1175061</t>
+          <t>1174884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1207267</t>
+          <t>1205441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61815</t>
+          <t>63714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70100</t>
+          <t>69335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95620</t>
+          <t>96572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>83850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149825</t>
+          <t>151192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1131049</t>
+          <t>1129150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1169220</t>
+          <t>1170125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>861817</t>
+          <t>860865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>887337</t>
+          <t>888102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2000476</t>
+          <t>1999109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2069442</t>
+          <t>2066451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73302</t>
+          <t>73076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>47332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95738</t>
+          <t>96320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667367</t>
+          <t>668075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>686127</t>
+          <t>686209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>859745</t>
+          <t>859971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>908694</t>
+          <t>907544</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1538594</t>
+          <t>1538012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1584053</t>
+          <t>1587000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29727</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53012</t>
+          <t>52808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62116</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94999</t>
+          <t>95754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101268</t>
+          <t>100937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139726</t>
+          <t>139192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873819</t>
+          <t>874023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>897104</t>
+          <t>896693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>996915</t>
+          <t>996160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029798</t>
+          <t>1029777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1879019</t>
+          <t>1879553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917477</t>
+          <t>1917808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>118186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177835</t>
+          <t>178489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239466</t>
+          <t>233275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319636</t>
+          <t>322918</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>390812</t>
+          <t>382468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>488338</t>
+          <t>485284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3278587</t>
+          <t>3277933</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3338164</t>
+          <t>3338236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3338132</t>
+          <t>3334850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3418302</t>
+          <t>3424493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6625852</t>
+          <t>6628906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6723378</t>
+          <t>6731722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1438_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45151</t>
+          <t>47768</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>61547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>74310</t>
+          <t>77372</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63878</t>
+          <t>65259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85812</t>
+          <t>90325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119462</t>
+          <t>125140</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105370</t>
+          <t>110367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135927</t>
+          <t>143369</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>590290</t>
+          <t>642942</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576565</t>
+          <t>629163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>600480</t>
+          <t>653854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>601060</t>
+          <t>655350</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>589558</t>
+          <t>642397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>611492</t>
+          <t>667463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1191349</t>
+          <t>1298291</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1174884</t>
+          <t>1280062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1205441</t>
+          <t>1313064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44342</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>35596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63714</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82863</t>
+          <t>91859</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>77889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96572</t>
+          <t>106874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>127205</t>
+          <t>139676</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83850</t>
+          <t>120267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151192</t>
+          <t>158721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1148522</t>
+          <t>1001100</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1129150</t>
+          <t>986278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1170125</t>
+          <t>1013321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>874574</t>
+          <t>978328</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>860865</t>
+          <t>963313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>888102</t>
+          <t>992298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2023096</t>
+          <t>1979428</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1999109</t>
+          <t>1960383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2066451</t>
+          <t>1998837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150301</t>
+          <t>2119104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>61318</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>49510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73076</t>
+          <t>76875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>75811</t>
+          <t>87348</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>72870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96320</t>
+          <t>103396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>678188</t>
+          <t>773318</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668075</t>
+          <t>761986</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>686209</t>
+          <t>781633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>880333</t>
+          <t>749589</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>859971</t>
+          <t>734032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>907544</t>
+          <t>761397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1558521</t>
+          <t>1522907</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1538012</t>
+          <t>1506859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1587000</t>
+          <t>1537385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701285</t>
+          <t>799348</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701285</t>
+          <t>799348</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701285</t>
+          <t>799348</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933047</t>
+          <t>810907</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933047</t>
+          <t>810907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933047</t>
+          <t>810907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634332</t>
+          <t>1610255</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634332</t>
+          <t>1610255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634332</t>
+          <t>1610255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40137</t>
+          <t>42113</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30138</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52808</t>
+          <t>55089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79453</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>75311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95754</t>
+          <t>104948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>119590</t>
+          <t>129898</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100937</t>
+          <t>112766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139192</t>
+          <t>149509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>886694</t>
+          <t>947949</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874023</t>
+          <t>934973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896693</t>
+          <t>957936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1012461</t>
+          <t>1029849</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>996160</t>
+          <t>1012686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029777</t>
+          <t>1042323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1899155</t>
+          <t>1977798</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1879553</t>
+          <t>1958187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917808</t>
+          <t>1994930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>142231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178489</t>
+          <t>187382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>289340</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>233275</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>322918</t>
+          <t>346789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>442068</t>
+          <t>482063</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>382468</t>
+          <t>448195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>485284</t>
+          <t>519194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3303694</t>
+          <t>3365308</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3277933</t>
+          <t>3341655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3338236</t>
+          <t>3386806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3368428</t>
+          <t>3413116</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3334850</t>
+          <t>3384661</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3424493</t>
+          <t>3436084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6672122</t>
+          <t>6778424</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6628906</t>
+          <t>6741293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6731722</t>
+          <t>6812292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
